--- a/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SAM_20260917.xlsx
+++ b/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SAM_20260917.xlsx
@@ -4228,7 +4228,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4268,6 +4268,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4896,7 +4902,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="8" applyBorder="1"/>
@@ -5381,6 +5387,19 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="0" borderId="0" xfId="0"/>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="0" xfId="0" applyFont="1"/>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="55" borderId="0" xfId="0" applyFont="1"/>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Normal 2 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -8200,136 +8219,136 @@
       </c>
     </row>
     <row r="12" spans="1:34" s="86" customFormat="1">
-      <c r="A12" s="85"/>
-      <c r="B12" s="81" t="str">
+      <c r="A12" s="180"/>
+      <c r="B12" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C12" s="82"/>
-      <c r="D12" s="81" t="inlineStr">
+      <c r="C12" s="178"/>
+      <c r="D12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0003</t>
         </is>
       </c>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81" t="inlineStr">
+      <c r="E12" s="177"/>
+      <c r="F12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-003</t>
         </is>
       </c>
-      <c r="G12" s="81" t="inlineStr">
+      <c r="G12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H12" s="81" t="inlineStr">
+      <c r="H12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Reception</t>
         </is>
       </c>
-      <c r="I12" s="81" t="inlineStr">
+      <c r="I12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">This function shall apply AuthData when it is found in USB storage
 (AuthData at the root of the USB external memory is received)</t>
         </is>
       </c>
-      <c r="J12" s="81" t="inlineStr">
+      <c r="J12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K12" s="81" t="inlineStr">
+      <c r="K12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L12" s="81" t="inlineStr">
+      <c r="L12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Insert USB drive containing the AuthData package into HU USB port
 2. Confirm the content of /data/vendor/dauth on the DUT
 $ adb shell ls -l /data/vendor/dauth</t>
         </is>
       </c>
-      <c r="M12" s="81" t="inlineStr">
+      <c r="M12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;SAM AuthData reception evidence provided by RD (X-g)&gt;
 2. The adb shell ls -l /data/vendor/dauth output lists the received AuthData</t>
         </is>
       </c>
-      <c r="N12" s="81" t="inlineStr">
+      <c r="N12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0003</t>
         </is>
       </c>
-      <c r="O12" s="81" t="inlineStr">
+      <c r="O12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P12" s="81" t="inlineStr">
+      <c r="P12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q12" s="81"/>
-      <c r="R12" s="81" t="inlineStr">
+      <c r="Q12" s="177"/>
+      <c r="R12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S12" s="81" t="inlineStr">
+      <c r="S12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T12" s="81" t="inlineStr">
+      <c r="T12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U12" s="81" t="inlineStr">
+      <c r="U12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V12" s="81" t="inlineStr">
+      <c r="V12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W12" s="81" t="inlineStr">
+      <c r="W12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X12" s="83" t="inlineStr">
+      <c r="X12" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y12" s="81" t="inlineStr">
+      <c r="Y12" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z12" s="83" t="inlineStr">
+      <c r="Z12" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA12" s="83" t="inlineStr">
+      <c r="AA12" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB12" s="81"/>
-      <c r="AC12" s="81"/>
-      <c r="AD12" s="81"/>
-      <c r="AE12" s="81"/>
-      <c r="AF12" s="81"/>
-      <c r="AG12" s="81"/>
-      <c r="AH12" s="83" t="inlineStr">
+      <c r="AB12" s="177"/>
+      <c r="AC12" s="177"/>
+      <c r="AD12" s="177"/>
+      <c r="AE12" s="177"/>
+      <c r="AF12" s="177"/>
+      <c r="AG12" s="177"/>
+      <c r="AH12" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0003 Requirement Description and Verification Criteria
 sibling axis: media layout
@@ -8339,51 +8358,51 @@
       </c>
     </row>
     <row r="13" spans="1:34">
-      <c r="A13" s="87"/>
-      <c r="B13" s="81" t="str">
+      <c r="A13" s="182"/>
+      <c r="B13" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C13" s="82"/>
-      <c r="D13" s="81" t="inlineStr">
+      <c r="C13" s="178"/>
+      <c r="D13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0003</t>
         </is>
       </c>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81" t="inlineStr">
+      <c r="E13" s="177"/>
+      <c r="F13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-004</t>
         </is>
       </c>
-      <c r="G13" s="81" t="inlineStr">
+      <c r="G13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H13" s="81" t="inlineStr">
+      <c r="H13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Reception</t>
         </is>
       </c>
-      <c r="I13" s="81" t="inlineStr">
+      <c r="I13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">This function shall apply AuthData when it is found in USB storage
 (AuthData not at the root of the USB external memory is not received)</t>
         </is>
       </c>
-      <c r="J13" s="81" t="inlineStr">
+      <c r="J13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K13" s="81" t="inlineStr">
+      <c r="K13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L13" s="81" t="inlineStr">
+      <c r="L13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;DUT-side trigger for SAM AuthData package outside the USB root provided by RD (X-g)&gt;
 $ &lt;command provided by RD (X-g)&gt;
@@ -8391,85 +8410,85 @@
 $ adb shell ls -l /data/vendor/dauth</t>
         </is>
       </c>
-      <c r="M13" s="81" t="inlineStr">
+      <c r="M13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;observable outcome provided by RD (X-g)&gt;
 2. The adb shell ls -l /data/vendor/dauth output lists no newly received AuthData</t>
         </is>
       </c>
-      <c r="N13" s="81" t="inlineStr">
+      <c r="N13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0003</t>
         </is>
       </c>
-      <c r="O13" s="81" t="inlineStr">
+      <c r="O13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P13" s="81" t="inlineStr">
+      <c r="P13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81" t="inlineStr">
+      <c r="Q13" s="177"/>
+      <c r="R13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">負向測試 (Negative / Invalid)</t>
         </is>
       </c>
-      <c r="S13" s="81" t="inlineStr">
+      <c r="S13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T13" s="81" t="inlineStr">
+      <c r="T13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U13" s="81" t="inlineStr">
+      <c r="U13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V13" s="81" t="inlineStr">
+      <c r="V13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W13" s="81" t="inlineStr">
+      <c r="W13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X13" s="83" t="inlineStr">
+      <c r="X13" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y13" s="81" t="inlineStr">
+      <c r="Y13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z13" s="83" t="inlineStr">
+      <c r="Z13" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA13" s="83" t="inlineStr">
+      <c r="AA13" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB13" s="81"/>
-      <c r="AC13" s="81"/>
-      <c r="AD13" s="81"/>
-      <c r="AE13" s="81"/>
-      <c r="AF13" s="81"/>
-      <c r="AG13" s="81"/>
-      <c r="AH13" s="83" t="inlineStr">
+      <c r="AB13" s="177"/>
+      <c r="AC13" s="177"/>
+      <c r="AD13" s="177"/>
+      <c r="AE13" s="177"/>
+      <c r="AF13" s="177"/>
+      <c r="AG13" s="177"/>
+      <c r="AH13" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0003 Requirement Description and Verification Criteria
 sibling axis: media layout
@@ -8480,40 +8499,40 @@
       </c>
     </row>
     <row r="14" spans="1:34">
-      <c r="A14" s="87"/>
-      <c r="B14" s="81" t="str">
+      <c r="A14" s="182"/>
+      <c r="B14" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C14" s="82"/>
-      <c r="D14" s="81" t="inlineStr">
+      <c r="C14" s="178"/>
+      <c r="D14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0004</t>
         </is>
       </c>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81" t="inlineStr">
+      <c r="E14" s="177"/>
+      <c r="F14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-005</t>
         </is>
       </c>
-      <c r="G14" s="81" t="inlineStr">
+      <c r="G14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H14" s="81" t="inlineStr">
+      <c r="H14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Error Handling</t>
         </is>
       </c>
-      <c r="I14" s="81" t="inlineStr">
+      <c r="I14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">DebugAuth just logs an error, if verification or ID check failed.
 (AuthData verification fails; the error is logged and the installed AuthData is retained)</t>
         </is>
       </c>
-      <c r="J14" s="81" t="inlineStr">
+      <c r="J14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. AuthData is already installed on the DUT
@@ -8521,12 +8540,12 @@
 4. A USB drive containing an AuthData package with a mismatching signature is available</t>
         </is>
       </c>
-      <c r="K14" s="81" t="inlineStr">
+      <c r="K14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L14" s="81" t="inlineStr">
+      <c r="L14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Record the content of /data/vendor/dauth on the DUT
 $ adb shell ls -l /data/vendor/dauth
@@ -8539,7 +8558,7 @@
 $ adb shell ls -l /data/vendor/dauth</t>
         </is>
       </c>
-      <c r="M14" s="81" t="inlineStr">
+      <c r="M14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The adb shell ls -l /data/vendor/dauth output lists the installed AuthData
 2. The log buffer is cleared
@@ -8548,79 +8567,79 @@
 5. The adb shell ls -l /data/vendor/dauth output lists the same installed AuthData as in step 1</t>
         </is>
       </c>
-      <c r="N14" s="81" t="inlineStr">
+      <c r="N14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0004</t>
         </is>
       </c>
-      <c r="O14" s="81" t="inlineStr">
+      <c r="O14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P14" s="81" t="inlineStr">
+      <c r="P14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q14" s="81"/>
-      <c r="R14" s="81" t="inlineStr">
+      <c r="Q14" s="177"/>
+      <c r="R14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">負向測試 (Negative / Invalid)</t>
         </is>
       </c>
-      <c r="S14" s="81" t="inlineStr">
+      <c r="S14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T14" s="81" t="inlineStr">
+      <c r="T14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U14" s="81" t="inlineStr">
+      <c r="U14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V14" s="81" t="inlineStr">
+      <c r="V14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W14" s="81" t="inlineStr">
+      <c r="W14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X14" s="83" t="inlineStr">
+      <c r="X14" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y14" s="81" t="inlineStr">
+      <c r="Y14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z14" s="83" t="inlineStr">
+      <c r="Z14" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA14" s="83" t="inlineStr">
+      <c r="AA14" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB14" s="81"/>
-      <c r="AC14" s="81"/>
-      <c r="AD14" s="81"/>
-      <c r="AE14" s="81"/>
-      <c r="AF14" s="81"/>
-      <c r="AG14" s="81"/>
-      <c r="AH14" s="83" t="inlineStr">
+      <c r="AB14" s="177"/>
+      <c r="AC14" s="177"/>
+      <c r="AD14" s="177"/>
+      <c r="AE14" s="177"/>
+      <c r="AF14" s="177"/>
+      <c r="AG14" s="177"/>
+      <c r="AH14" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0004 Requirement Description and Verification Criteria
 sibling axis: verification outcome; rule 1,4 of SEC-04 4.2
@@ -8631,51 +8650,51 @@
       </c>
     </row>
     <row r="15" spans="1:34">
-      <c r="A15" s="87"/>
-      <c r="B15" s="81" t="str">
+      <c r="A15" s="182"/>
+      <c r="B15" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C15" s="82"/>
-      <c r="D15" s="81" t="inlineStr">
+      <c r="C15" s="178"/>
+      <c r="D15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0005</t>
         </is>
       </c>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81" t="inlineStr">
+      <c r="E15" s="177"/>
+      <c r="F15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-006</t>
         </is>
       </c>
-      <c r="G15" s="81" t="inlineStr">
+      <c r="G15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H15" s="81" t="inlineStr">
+      <c r="H15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Verification</t>
         </is>
       </c>
-      <c r="I15" s="81" t="inlineStr">
+      <c r="I15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">DebugAuth shall verify received files and rejects them if verification fails.
 (manifest, SAM certificate and manifest signature are all valid)</t>
         </is>
       </c>
-      <c r="J15" s="81" t="inlineStr">
+      <c r="J15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K15" s="81" t="inlineStr">
+      <c r="K15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L15" s="81" t="inlineStr">
+      <c r="L15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Read the SAM certificate on the host
 $ openssl x509 -in SAMcert.pem -text
@@ -8687,7 +8706,7 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M15" s="81" t="inlineStr">
+      <c r="M15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The openssl x509 output shows the certificate in x509 PEM format
 2. The openssl command prints "SAMcert.pem: OK" on stdout
@@ -8695,79 +8714,79 @@
 4. The adb logcat -s dauth output contains the successful verification entry</t>
         </is>
       </c>
-      <c r="N15" s="81" t="inlineStr">
+      <c r="N15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0005</t>
         </is>
       </c>
-      <c r="O15" s="81" t="inlineStr">
+      <c r="O15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P15" s="81" t="inlineStr">
+      <c r="P15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q15" s="81"/>
-      <c r="R15" s="81" t="inlineStr">
+      <c r="Q15" s="177"/>
+      <c r="R15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S15" s="81" t="inlineStr">
+      <c r="S15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T15" s="81" t="inlineStr">
+      <c r="T15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U15" s="81" t="inlineStr">
+      <c r="U15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V15" s="81" t="inlineStr">
+      <c r="V15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W15" s="81" t="inlineStr">
+      <c r="W15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X15" s="83" t="inlineStr">
+      <c r="X15" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y15" s="81" t="inlineStr">
+      <c r="Y15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z15" s="83" t="inlineStr">
+      <c r="Z15" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA15" s="83" t="inlineStr">
+      <c r="AA15" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB15" s="81"/>
-      <c r="AC15" s="81"/>
-      <c r="AD15" s="81"/>
-      <c r="AE15" s="81"/>
-      <c r="AF15" s="81"/>
-      <c r="AG15" s="81"/>
-      <c r="AH15" s="83" t="inlineStr">
+      <c r="AB15" s="177"/>
+      <c r="AC15" s="177"/>
+      <c r="AD15" s="177"/>
+      <c r="AE15" s="177"/>
+      <c r="AF15" s="177"/>
+      <c r="AG15" s="177"/>
+      <c r="AH15" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0005 Requirement Description and Verification Criteria
 sibling axis: verification outcome
@@ -8778,51 +8797,51 @@
       </c>
     </row>
     <row r="16" spans="1:34">
-      <c r="A16" s="87"/>
-      <c r="B16" s="81" t="str">
+      <c r="A16" s="182"/>
+      <c r="B16" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C16" s="82"/>
-      <c r="D16" s="81" t="inlineStr">
+      <c r="C16" s="178"/>
+      <c r="D16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0005</t>
         </is>
       </c>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81" t="inlineStr">
+      <c r="E16" s="177"/>
+      <c r="F16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-007</t>
         </is>
       </c>
-      <c r="G16" s="81" t="inlineStr">
+      <c r="G16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H16" s="81" t="inlineStr">
+      <c r="H16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Verification</t>
         </is>
       </c>
-      <c r="I16" s="81" t="inlineStr">
+      <c r="I16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">DebugAuth shall verify received files and rejects them if verification fails.
 (manifest signature is invalid; verification fails)</t>
         </is>
       </c>
-      <c r="J16" s="81" t="inlineStr">
+      <c r="J16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K16" s="81" t="inlineStr">
+      <c r="K16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L16" s="81" t="inlineStr">
+      <c r="L16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;DUT-side trigger for SAM AuthData package with an invalid manifest signature provided by RD (X-g)&gt;
 $ &lt;command provided by RD (X-g)&gt;
@@ -8830,85 +8849,85 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M16" s="81" t="inlineStr">
+      <c r="M16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;observable outcome provided by RD (X-g)&gt;
 2. &lt;log keyword provided by RD (X-h)&gt;</t>
         </is>
       </c>
-      <c r="N16" s="81" t="inlineStr">
+      <c r="N16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0005</t>
         </is>
       </c>
-      <c r="O16" s="81" t="inlineStr">
+      <c r="O16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P16" s="81" t="inlineStr">
+      <c r="P16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81" t="inlineStr">
+      <c r="Q16" s="177"/>
+      <c r="R16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">負向測試 (Negative / Invalid)</t>
         </is>
       </c>
-      <c r="S16" s="81" t="inlineStr">
+      <c r="S16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T16" s="81" t="inlineStr">
+      <c r="T16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U16" s="81" t="inlineStr">
+      <c r="U16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V16" s="81" t="inlineStr">
+      <c r="V16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W16" s="81" t="inlineStr">
+      <c r="W16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X16" s="83" t="inlineStr">
+      <c r="X16" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y16" s="81" t="inlineStr">
+      <c r="Y16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z16" s="83" t="inlineStr">
+      <c r="Z16" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA16" s="83" t="inlineStr">
+      <c r="AA16" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="83" t="inlineStr">
+      <c r="AB16" s="177"/>
+      <c r="AC16" s="177"/>
+      <c r="AD16" s="177"/>
+      <c r="AE16" s="177"/>
+      <c r="AF16" s="177"/>
+      <c r="AG16" s="177"/>
+      <c r="AH16" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0005 Requirement Description and Verification Criteria
 sibling axis: verification outcome
@@ -8920,51 +8939,51 @@
       </c>
     </row>
     <row r="17" spans="1:34">
-      <c r="A17" s="87"/>
-      <c r="B17" s="81" t="str">
+      <c r="A17" s="182"/>
+      <c r="B17" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C17" s="82"/>
-      <c r="D17" s="81" t="inlineStr">
+      <c r="C17" s="178"/>
+      <c r="D17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0006</t>
         </is>
       </c>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81" t="inlineStr">
+      <c r="E17" s="177"/>
+      <c r="F17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-008</t>
         </is>
       </c>
-      <c r="G17" s="81" t="inlineStr">
+      <c r="G17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H17" s="81" t="inlineStr">
+      <c r="H17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Verification</t>
         </is>
       </c>
-      <c r="I17" s="81" t="inlineStr">
+      <c r="I17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">DebugAuth should compare "ECUId" from the received configuration to its own SSN (security serial number)
 (head unit serial number is the same as the ECUId parameter)</t>
         </is>
       </c>
-      <c r="J17" s="81" t="inlineStr">
+      <c r="J17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K17" s="81" t="inlineStr">
+      <c r="K17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L17" s="81" t="inlineStr">
+      <c r="L17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Read /sys/devices/soc0/serial_number on the DUT
 $ adb shell cat /sys/devices/soc0/serial_number
@@ -8974,86 +8993,86 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M17" s="81" t="inlineStr">
+      <c r="M17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The adb shell cat /sys/devices/soc0/serial_number output shows the head unit serial number
 2. &lt;observable outcome provided by RD (X-g)&gt;
 3. The adb logcat -s dauth output contains the serial number match entry</t>
         </is>
       </c>
-      <c r="N17" s="81" t="inlineStr">
+      <c r="N17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0006</t>
         </is>
       </c>
-      <c r="O17" s="81" t="inlineStr">
+      <c r="O17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P17" s="81" t="inlineStr">
+      <c r="P17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q17" s="81"/>
-      <c r="R17" s="81" t="inlineStr">
+      <c r="Q17" s="177"/>
+      <c r="R17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S17" s="81" t="inlineStr">
+      <c r="S17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T17" s="81" t="inlineStr">
+      <c r="T17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U17" s="81" t="inlineStr">
+      <c r="U17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V17" s="81" t="inlineStr">
+      <c r="V17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W17" s="81" t="inlineStr">
+      <c r="W17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X17" s="83" t="inlineStr">
+      <c r="X17" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y17" s="81" t="inlineStr">
+      <c r="Y17" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z17" s="83" t="inlineStr">
+      <c r="Z17" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA17" s="83" t="inlineStr">
+      <c r="AA17" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB17" s="81"/>
-      <c r="AC17" s="81"/>
-      <c r="AD17" s="81"/>
-      <c r="AE17" s="81"/>
-      <c r="AF17" s="81"/>
-      <c r="AG17" s="81"/>
-      <c r="AH17" s="83" t="inlineStr">
+      <c r="AB17" s="177"/>
+      <c r="AC17" s="177"/>
+      <c r="AD17" s="177"/>
+      <c r="AE17" s="177"/>
+      <c r="AF17" s="177"/>
+      <c r="AG17" s="177"/>
+      <c r="AH17" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0006 Requirement Description and Verification Criteria
 sibling axis: serial match
@@ -9064,51 +9083,51 @@
       </c>
     </row>
     <row r="18" spans="1:34">
-      <c r="A18" s="87"/>
-      <c r="B18" s="81" t="str">
+      <c r="A18" s="182"/>
+      <c r="B18" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C18" s="82"/>
-      <c r="D18" s="81" t="inlineStr">
+      <c r="C18" s="178"/>
+      <c r="D18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0006</t>
         </is>
       </c>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81" t="inlineStr">
+      <c r="E18" s="177"/>
+      <c r="F18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-009</t>
         </is>
       </c>
-      <c r="G18" s="81" t="inlineStr">
+      <c r="G18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H18" s="81" t="inlineStr">
+      <c r="H18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Verification</t>
         </is>
       </c>
-      <c r="I18" s="81" t="inlineStr">
+      <c r="I18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">DebugAuth should compare "ECUId" from the received configuration to its own SSN (security serial number)
 (head unit serial number differs from the ECUId parameter)</t>
         </is>
       </c>
-      <c r="J18" s="81" t="inlineStr">
+      <c r="J18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K18" s="81" t="inlineStr">
+      <c r="K18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L18" s="81" t="inlineStr">
+      <c r="L18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;DUT-side trigger for SAM AuthData package issued for another serial number provided by RD (X-g)&gt;
 $ &lt;command provided by RD (X-g)&gt;
@@ -9116,85 +9135,85 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M18" s="81" t="inlineStr">
+      <c r="M18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;observable outcome provided by RD (X-g)&gt;
 2. &lt;log keyword provided by RD (X-h)&gt;</t>
         </is>
       </c>
-      <c r="N18" s="81" t="inlineStr">
+      <c r="N18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0006</t>
         </is>
       </c>
-      <c r="O18" s="81" t="inlineStr">
+      <c r="O18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P18" s="81" t="inlineStr">
+      <c r="P18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="81" t="inlineStr">
+      <c r="Q18" s="177"/>
+      <c r="R18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">負向測試 (Negative / Invalid)</t>
         </is>
       </c>
-      <c r="S18" s="81" t="inlineStr">
+      <c r="S18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T18" s="81" t="inlineStr">
+      <c r="T18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U18" s="81" t="inlineStr">
+      <c r="U18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V18" s="81" t="inlineStr">
+      <c r="V18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W18" s="81" t="inlineStr">
+      <c r="W18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X18" s="83" t="inlineStr">
+      <c r="X18" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y18" s="81" t="inlineStr">
+      <c r="Y18" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z18" s="83" t="inlineStr">
+      <c r="Z18" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA18" s="83" t="inlineStr">
+      <c r="AA18" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB18" s="81"/>
-      <c r="AC18" s="81"/>
-      <c r="AD18" s="81"/>
-      <c r="AE18" s="81"/>
-      <c r="AF18" s="81"/>
-      <c r="AG18" s="81"/>
-      <c r="AH18" s="83" t="inlineStr">
+      <c r="AB18" s="177"/>
+      <c r="AC18" s="177"/>
+      <c r="AD18" s="177"/>
+      <c r="AE18" s="177"/>
+      <c r="AF18" s="177"/>
+      <c r="AG18" s="177"/>
+      <c r="AH18" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0006 Requirement Description and Verification Criteria
 sibling axis: serial match
@@ -9351,40 +9370,40 @@
       </c>
     </row>
     <row r="20" spans="1:34">
-      <c r="A20" s="87"/>
-      <c r="B20" s="81" t="str">
+      <c r="A20" s="182"/>
+      <c r="B20" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="81" t="inlineStr">
+      <c r="C20" s="178"/>
+      <c r="D20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0007</t>
         </is>
       </c>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81" t="inlineStr">
+      <c r="E20" s="177"/>
+      <c r="F20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-011</t>
         </is>
       </c>
-      <c r="G20" s="81" t="inlineStr">
+      <c r="G20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H20" s="81" t="inlineStr">
+      <c r="H20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Verification</t>
         </is>
       </c>
-      <c r="I20" s="81" t="inlineStr">
+      <c r="I20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">DebugAuth shall check SAM certificate as part of AuthData verification.
 (SAM certificate does not anchor to the OEM issued root; verification fails)</t>
         </is>
       </c>
-      <c r="J20" s="81" t="inlineStr">
+      <c r="J20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. Test runner CertProviderAndroidInstrumentalTest.apk is installed
@@ -9392,12 +9411,12 @@
 4. An AuthData package is available on a USB drive</t>
         </is>
       </c>
-      <c r="K20" s="81" t="inlineStr">
+      <c r="K20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L20" s="81" t="inlineStr">
+      <c r="L20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Read the SAM certificate format and subject on the host
 $ openssl x509 -in SAMcert.pem -text
@@ -9407,86 +9426,86 @@
 $ &lt;command provided by RD (X-g)&gt;</t>
         </is>
       </c>
-      <c r="M20" s="81" t="inlineStr">
+      <c r="M20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The openssl x509 output shows an "Issuer:" line that does not anchor to the OEM issued root certificate
 2. The openssl command prints "unable to get issuer certificate" on stdout
 3. &lt;log keyword provided by RD (X-h)&gt;</t>
         </is>
       </c>
-      <c r="N20" s="81" t="inlineStr">
+      <c r="N20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0007</t>
         </is>
       </c>
-      <c r="O20" s="81" t="inlineStr">
+      <c r="O20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P20" s="81" t="inlineStr">
+      <c r="P20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q20" s="81"/>
-      <c r="R20" s="81" t="inlineStr">
+      <c r="Q20" s="177"/>
+      <c r="R20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">負向測試 (Negative / Invalid)</t>
         </is>
       </c>
-      <c r="S20" s="81" t="inlineStr">
+      <c r="S20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T20" s="81" t="inlineStr">
+      <c r="T20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U20" s="81" t="inlineStr">
+      <c r="U20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V20" s="81" t="inlineStr">
+      <c r="V20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W20" s="81" t="inlineStr">
+      <c r="W20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X20" s="83" t="inlineStr">
+      <c r="X20" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y20" s="81" t="inlineStr">
+      <c r="Y20" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z20" s="83" t="inlineStr">
+      <c r="Z20" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA20" s="83" t="inlineStr">
+      <c r="AA20" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB20" s="81"/>
-      <c r="AC20" s="81"/>
-      <c r="AD20" s="81"/>
-      <c r="AE20" s="81"/>
-      <c r="AF20" s="81"/>
-      <c r="AG20" s="81"/>
-      <c r="AH20" s="83" t="inlineStr">
+      <c r="AB20" s="177"/>
+      <c r="AC20" s="177"/>
+      <c r="AD20" s="177"/>
+      <c r="AE20" s="177"/>
+      <c r="AF20" s="177"/>
+      <c r="AG20" s="177"/>
+      <c r="AH20" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0007 Requirement Description and Verification Criteria
 sibling axis: certificate validity; rule 3 of SEC-04 4.2
@@ -9636,51 +9655,51 @@
       </c>
     </row>
     <row r="22" spans="1:34">
-      <c r="A22" s="87"/>
-      <c r="B22" s="81" t="str">
+      <c r="A22" s="182"/>
+      <c r="B22" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C22" s="82"/>
-      <c r="D22" s="81" t="inlineStr">
+      <c r="C22" s="178"/>
+      <c r="D22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0008</t>
         </is>
       </c>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81" t="inlineStr">
+      <c r="E22" s="177"/>
+      <c r="F22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-013</t>
         </is>
       </c>
-      <c r="G22" s="81" t="inlineStr">
+      <c r="G22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H22" s="81" t="inlineStr">
+      <c r="H22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Verification</t>
         </is>
       </c>
-      <c r="I22" s="81" t="inlineStr">
+      <c r="I22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData contains Manifest file, manifest signature and SAM certificate file.
 (manifest file format is invalid; the package is not accepted)</t>
         </is>
       </c>
-      <c r="J22" s="81" t="inlineStr">
+      <c r="J22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K22" s="81" t="inlineStr">
+      <c r="K22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L22" s="81" t="inlineStr">
+      <c r="L22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;DUT-side trigger for SAM AuthData package with a malformed manifest provided by RD (X-g)&gt;
 $ &lt;command provided by RD (X-g)&gt;
@@ -9688,85 +9707,85 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M22" s="81" t="inlineStr">
+      <c r="M22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;observable outcome provided by RD (X-g)&gt;
 2. &lt;log keyword provided by RD (X-h)&gt;</t>
         </is>
       </c>
-      <c r="N22" s="81" t="inlineStr">
+      <c r="N22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0008</t>
         </is>
       </c>
-      <c r="O22" s="81" t="inlineStr">
+      <c r="O22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P22" s="81" t="inlineStr">
+      <c r="P22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="Q22" s="81"/>
-      <c r="R22" s="81" t="inlineStr">
+      <c r="Q22" s="177"/>
+      <c r="R22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">負向測試 (Negative / Invalid)</t>
         </is>
       </c>
-      <c r="S22" s="81" t="inlineStr">
+      <c r="S22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T22" s="81" t="inlineStr">
+      <c r="T22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U22" s="81" t="inlineStr">
+      <c r="U22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V22" s="81" t="inlineStr">
+      <c r="V22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W22" s="81" t="inlineStr">
+      <c r="W22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X22" s="83" t="inlineStr">
+      <c r="X22" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y22" s="81" t="inlineStr">
+      <c r="Y22" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z22" s="83" t="inlineStr">
+      <c r="Z22" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA22" s="83" t="inlineStr">
+      <c r="AA22" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB22" s="81"/>
-      <c r="AC22" s="81"/>
-      <c r="AD22" s="81"/>
-      <c r="AE22" s="81"/>
-      <c r="AF22" s="81"/>
-      <c r="AG22" s="81"/>
-      <c r="AH22" s="83" t="inlineStr">
+      <c r="AB22" s="177"/>
+      <c r="AC22" s="177"/>
+      <c r="AD22" s="177"/>
+      <c r="AE22" s="177"/>
+      <c r="AF22" s="177"/>
+      <c r="AG22" s="177"/>
+      <c r="AH22" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0008 Requirement Description and Verification Criteria
 sibling axis: package format
@@ -9778,51 +9797,51 @@
       </c>
     </row>
     <row r="23" spans="1:34">
-      <c r="A23" s="87"/>
-      <c r="B23" s="81" t="str">
+      <c r="A23" s="182"/>
+      <c r="B23" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C23" s="82"/>
-      <c r="D23" s="81" t="inlineStr">
+      <c r="C23" s="178"/>
+      <c r="D23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0009</t>
         </is>
       </c>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81" t="inlineStr">
+      <c r="E23" s="177"/>
+      <c r="F23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-014</t>
         </is>
       </c>
-      <c r="G23" s="81" t="inlineStr">
+      <c r="G23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H23" s="81" t="inlineStr">
+      <c r="H23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Installation</t>
         </is>
       </c>
-      <c r="I23" s="81" t="inlineStr">
+      <c r="I23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">When "Install" option is true in
 (Install is true and SAMType is not Logging; AuthData is copied to the secure storage)</t>
         </is>
       </c>
-      <c r="J23" s="81" t="inlineStr">
+      <c r="J23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K23" s="81" t="inlineStr">
+      <c r="K23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L23" s="81" t="inlineStr">
+      <c r="L23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;DUT-side trigger for SAM AuthData package with Install true and a non-Logging SAMType provided by RD (X-g)&gt;
 $ &lt;command provided by RD (X-g)&gt;
@@ -9830,85 +9849,85 @@
 $ adb shell ls -l /data/vendor/dauth</t>
         </is>
       </c>
-      <c r="M23" s="81" t="inlineStr">
+      <c r="M23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;observable outcome provided by RD (X-g)&gt;
 2. The adb shell ls -l /data/vendor/dauth output lists the copied AuthData</t>
         </is>
       </c>
-      <c r="N23" s="81" t="inlineStr">
+      <c r="N23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0009</t>
         </is>
       </c>
-      <c r="O23" s="81" t="inlineStr">
+      <c r="O23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P23" s="81" t="inlineStr">
+      <c r="P23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q23" s="81"/>
-      <c r="R23" s="81" t="inlineStr">
+      <c r="Q23" s="177"/>
+      <c r="R23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S23" s="81" t="inlineStr">
+      <c r="S23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T23" s="81" t="inlineStr">
+      <c r="T23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U23" s="81" t="inlineStr">
+      <c r="U23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V23" s="81" t="inlineStr">
+      <c r="V23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W23" s="81" t="inlineStr">
+      <c r="W23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X23" s="83" t="inlineStr">
+      <c r="X23" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y23" s="81" t="inlineStr">
+      <c r="Y23" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z23" s="83" t="inlineStr">
+      <c r="Z23" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA23" s="83" t="inlineStr">
+      <c r="AA23" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB23" s="81"/>
-      <c r="AC23" s="81"/>
-      <c r="AD23" s="81"/>
-      <c r="AE23" s="81"/>
-      <c r="AF23" s="81"/>
-      <c r="AG23" s="81"/>
-      <c r="AH23" s="83" t="inlineStr">
+      <c r="AB23" s="177"/>
+      <c r="AC23" s="177"/>
+      <c r="AD23" s="177"/>
+      <c r="AE23" s="177"/>
+      <c r="AF23" s="177"/>
+      <c r="AG23" s="177"/>
+      <c r="AH23" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0009 Requirement Description and Verification Criteria
 sibling axis: install option
@@ -9919,51 +9938,51 @@
       </c>
     </row>
     <row r="24" spans="1:34">
-      <c r="A24" s="87"/>
-      <c r="B24" s="81" t="str">
+      <c r="A24" s="182"/>
+      <c r="B24" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C24" s="82"/>
-      <c r="D24" s="81" t="inlineStr">
+      <c r="C24" s="178"/>
+      <c r="D24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0009</t>
         </is>
       </c>
-      <c r="E24" s="81"/>
-      <c r="F24" s="81" t="inlineStr">
+      <c r="E24" s="177"/>
+      <c r="F24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-015</t>
         </is>
       </c>
-      <c r="G24" s="81" t="inlineStr">
+      <c r="G24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H24" s="81" t="inlineStr">
+      <c r="H24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Installation</t>
         </is>
       </c>
-      <c r="I24" s="81" t="inlineStr">
+      <c r="I24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">When "Install" option is true in
 (SAMType is Logging; AuthData is not copied to the secure storage)</t>
         </is>
       </c>
-      <c r="J24" s="81" t="inlineStr">
+      <c r="J24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K24" s="81" t="inlineStr">
+      <c r="K24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L24" s="81" t="inlineStr">
+      <c r="L24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;DUT-side trigger for SAM AuthData package with a Logging SAMType provided by RD (X-g)&gt;
 $ &lt;command provided by RD (X-g)&gt;
@@ -9971,85 +9990,85 @@
 $ adb shell ls -l /data/vendor/dauth</t>
         </is>
       </c>
-      <c r="M24" s="81" t="inlineStr">
+      <c r="M24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;observable outcome provided by RD (X-g)&gt;
 2. The adb shell ls -l /data/vendor/dauth output lists no copied AuthData</t>
         </is>
       </c>
-      <c r="N24" s="81" t="inlineStr">
+      <c r="N24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0009</t>
         </is>
       </c>
-      <c r="O24" s="81" t="inlineStr">
+      <c r="O24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P24" s="81" t="inlineStr">
+      <c r="P24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q24" s="81"/>
-      <c r="R24" s="81" t="inlineStr">
+      <c r="Q24" s="177"/>
+      <c r="R24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">負向測試 (Negative / Invalid)</t>
         </is>
       </c>
-      <c r="S24" s="81" t="inlineStr">
+      <c r="S24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T24" s="81" t="inlineStr">
+      <c r="T24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U24" s="81" t="inlineStr">
+      <c r="U24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V24" s="81" t="inlineStr">
+      <c r="V24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W24" s="81" t="inlineStr">
+      <c r="W24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X24" s="83" t="inlineStr">
+      <c r="X24" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y24" s="81" t="inlineStr">
+      <c r="Y24" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z24" s="83" t="inlineStr">
+      <c r="Z24" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA24" s="83" t="inlineStr">
+      <c r="AA24" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB24" s="81"/>
-      <c r="AC24" s="81"/>
-      <c r="AD24" s="81"/>
-      <c r="AE24" s="81"/>
-      <c r="AF24" s="81"/>
-      <c r="AG24" s="81"/>
-      <c r="AH24" s="83" t="inlineStr">
+      <c r="AB24" s="177"/>
+      <c r="AC24" s="177"/>
+      <c r="AD24" s="177"/>
+      <c r="AE24" s="177"/>
+      <c r="AF24" s="177"/>
+      <c r="AG24" s="177"/>
+      <c r="AH24" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0009 Requirement Description and Verification Criteria
 sibling axis: install option
@@ -10060,51 +10079,51 @@
       </c>
     </row>
     <row r="25" spans="1:34">
-      <c r="A25" s="87"/>
-      <c r="B25" s="81" t="str">
+      <c r="A25" s="182"/>
+      <c r="B25" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C25" s="82"/>
-      <c r="D25" s="81" t="inlineStr">
+      <c r="C25" s="178"/>
+      <c r="D25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0010</t>
         </is>
       </c>
-      <c r="E25" s="81"/>
-      <c r="F25" s="81" t="inlineStr">
+      <c r="E25" s="177"/>
+      <c r="F25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-016</t>
         </is>
       </c>
-      <c r="G25" s="81" t="inlineStr">
+      <c r="G25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H25" s="81" t="inlineStr">
+      <c r="H25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Verification</t>
         </is>
       </c>
-      <c r="I25" s="81" t="inlineStr">
+      <c r="I25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Timestamp is a number but stored as string in configuration file
 (TimeStamp is greater than or equal to the stored value; AuthData is accepted)</t>
         </is>
       </c>
-      <c r="J25" s="81" t="inlineStr">
+      <c r="J25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K25" s="81" t="inlineStr">
+      <c r="K25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L25" s="81" t="inlineStr">
+      <c r="L25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Read /data/vendor/dauth/ts on the DUT
 $ adb shell cat /data/vendor/dauth/ts
@@ -10114,86 +10133,86 @@
 $ adb shell cat /data/vendor/dauth/ts</t>
         </is>
       </c>
-      <c r="M25" s="81" t="inlineStr">
+      <c r="M25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The adb shell cat /data/vendor/dauth/ts output shows the stored timestamp
 2. &lt;observable outcome provided by RD (X-g)&gt;
 3. The adb shell cat /data/vendor/dauth/ts output shows the updated timestamp</t>
         </is>
       </c>
-      <c r="N25" s="81" t="inlineStr">
+      <c r="N25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0010</t>
         </is>
       </c>
-      <c r="O25" s="81" t="inlineStr">
+      <c r="O25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P25" s="81" t="inlineStr">
+      <c r="P25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q25" s="81"/>
-      <c r="R25" s="81" t="inlineStr">
+      <c r="Q25" s="177"/>
+      <c r="R25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S25" s="81" t="inlineStr">
+      <c r="S25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T25" s="81" t="inlineStr">
+      <c r="T25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U25" s="81" t="inlineStr">
+      <c r="U25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V25" s="81" t="inlineStr">
+      <c r="V25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W25" s="81" t="inlineStr">
+      <c r="W25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X25" s="83" t="inlineStr">
+      <c r="X25" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y25" s="81" t="inlineStr">
+      <c r="Y25" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z25" s="83" t="inlineStr">
+      <c r="Z25" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA25" s="83" t="inlineStr">
+      <c r="AA25" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB25" s="81"/>
-      <c r="AC25" s="81"/>
-      <c r="AD25" s="81"/>
-      <c r="AE25" s="81"/>
-      <c r="AF25" s="81"/>
-      <c r="AG25" s="81"/>
-      <c r="AH25" s="83" t="inlineStr">
+      <c r="AB25" s="177"/>
+      <c r="AC25" s="177"/>
+      <c r="AD25" s="177"/>
+      <c r="AE25" s="177"/>
+      <c r="AF25" s="177"/>
+      <c r="AG25" s="177"/>
+      <c r="AH25" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0010 Requirement Description and Verification Criteria
 sibling axis: timestamp order
@@ -10204,51 +10223,51 @@
       </c>
     </row>
     <row r="26" spans="1:34">
-      <c r="A26" s="87"/>
-      <c r="B26" s="81" t="str">
+      <c r="A26" s="182"/>
+      <c r="B26" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C26" s="82"/>
-      <c r="D26" s="81" t="inlineStr">
+      <c r="C26" s="178"/>
+      <c r="D26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0010</t>
         </is>
       </c>
-      <c r="E26" s="81"/>
-      <c r="F26" s="81" t="inlineStr">
+      <c r="E26" s="177"/>
+      <c r="F26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-017</t>
         </is>
       </c>
-      <c r="G26" s="81" t="inlineStr">
+      <c r="G26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H26" s="81" t="inlineStr">
+      <c r="H26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Verification</t>
         </is>
       </c>
-      <c r="I26" s="81" t="inlineStr">
+      <c r="I26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Timestamp is a number but stored as string in configuration file
 (TimeStamp is older than the stored value; AuthData is rejected)</t>
         </is>
       </c>
-      <c r="J26" s="81" t="inlineStr">
+      <c r="J26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K26" s="81" t="inlineStr">
+      <c r="K26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L26" s="81" t="inlineStr">
+      <c r="L26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Read /data/vendor/dauth/ts on the DUT
 $ adb shell cat /data/vendor/dauth/ts
@@ -10258,86 +10277,86 @@
 $ adb shell cat /data/vendor/dauth/ts</t>
         </is>
       </c>
-      <c r="M26" s="81" t="inlineStr">
+      <c r="M26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The adb shell cat /data/vendor/dauth/ts output shows the stored timestamp
 2. &lt;observable outcome provided by RD (X-g)&gt;
 3. The adb shell cat /data/vendor/dauth/ts output shows the unchanged timestamp</t>
         </is>
       </c>
-      <c r="N26" s="81" t="inlineStr">
+      <c r="N26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0010</t>
         </is>
       </c>
-      <c r="O26" s="81" t="inlineStr">
+      <c r="O26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P26" s="81" t="inlineStr">
+      <c r="P26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q26" s="81"/>
-      <c r="R26" s="81" t="inlineStr">
+      <c r="Q26" s="177"/>
+      <c r="R26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">負向測試 (Negative / Invalid)</t>
         </is>
       </c>
-      <c r="S26" s="81" t="inlineStr">
+      <c r="S26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T26" s="81" t="inlineStr">
+      <c r="T26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U26" s="81" t="inlineStr">
+      <c r="U26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V26" s="81" t="inlineStr">
+      <c r="V26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W26" s="81" t="inlineStr">
+      <c r="W26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X26" s="83" t="inlineStr">
+      <c r="X26" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y26" s="81" t="inlineStr">
+      <c r="Y26" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z26" s="83" t="inlineStr">
+      <c r="Z26" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA26" s="83" t="inlineStr">
+      <c r="AA26" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB26" s="81"/>
-      <c r="AC26" s="81"/>
-      <c r="AD26" s="81"/>
-      <c r="AE26" s="81"/>
-      <c r="AF26" s="81"/>
-      <c r="AG26" s="81"/>
-      <c r="AH26" s="83" t="inlineStr">
+      <c r="AB26" s="177"/>
+      <c r="AC26" s="177"/>
+      <c r="AD26" s="177"/>
+      <c r="AE26" s="177"/>
+      <c r="AF26" s="177"/>
+      <c r="AG26" s="177"/>
+      <c r="AH26" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0010 Requirement Description and Verification Criteria
 sibling axis: timestamp order
@@ -10348,51 +10367,51 @@
       </c>
     </row>
     <row r="27" spans="1:34">
-      <c r="A27" s="87"/>
-      <c r="B27" s="81" t="str">
+      <c r="A27" s="182"/>
+      <c r="B27" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C27" s="82"/>
-      <c r="D27" s="81" t="inlineStr">
+      <c r="C27" s="178"/>
+      <c r="D27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0011</t>
         </is>
       </c>
-      <c r="E27" s="81"/>
-      <c r="F27" s="81" t="inlineStr">
+      <c r="E27" s="177"/>
+      <c r="F27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-018</t>
         </is>
       </c>
-      <c r="G27" s="81" t="inlineStr">
+      <c r="G27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H27" s="81" t="inlineStr">
+      <c r="H27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Installation</t>
         </is>
       </c>
-      <c r="I27" s="81" t="inlineStr">
+      <c r="I27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">DebugAuth shall reject and delete stored AuthData when verification of AuthData which located on secure non-volatile memory failed
 (verification of the stored AuthData fails; the stored AuthData is deleted)</t>
         </is>
       </c>
-      <c r="J27" s="81" t="inlineStr">
+      <c r="J27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K27" s="81" t="inlineStr">
+      <c r="K27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L27" s="81" t="inlineStr">
+      <c r="L27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Record the content of /data/vendor/dauth on the DUT
 $ adb shell ls -l /data/vendor/dauth
@@ -10402,86 +10421,86 @@
 $ adb shell ls -l /data/vendor/dauth</t>
         </is>
       </c>
-      <c r="M27" s="81" t="inlineStr">
+      <c r="M27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The adb shell ls -l /data/vendor/dauth output lists the stored AuthData
 2. &lt;observable outcome provided by RD (X-g)&gt;
 3. The adb shell ls -l /data/vendor/dauth output lists no stored AuthData</t>
         </is>
       </c>
-      <c r="N27" s="81" t="inlineStr">
+      <c r="N27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0011</t>
         </is>
       </c>
-      <c r="O27" s="81" t="inlineStr">
+      <c r="O27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P27" s="81" t="inlineStr">
+      <c r="P27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q27" s="81"/>
-      <c r="R27" s="81" t="inlineStr">
+      <c r="Q27" s="177"/>
+      <c r="R27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">負向測試 (Negative / Invalid)</t>
         </is>
       </c>
-      <c r="S27" s="81" t="inlineStr">
+      <c r="S27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T27" s="81" t="inlineStr">
+      <c r="T27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U27" s="81" t="inlineStr">
+      <c r="U27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V27" s="81" t="inlineStr">
+      <c r="V27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W27" s="81" t="inlineStr">
+      <c r="W27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X27" s="83" t="inlineStr">
+      <c r="X27" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y27" s="81" t="inlineStr">
+      <c r="Y27" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z27" s="83" t="inlineStr">
+      <c r="Z27" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA27" s="83" t="inlineStr">
+      <c r="AA27" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB27" s="81"/>
-      <c r="AC27" s="81"/>
-      <c r="AD27" s="81"/>
-      <c r="AE27" s="81"/>
-      <c r="AF27" s="81"/>
-      <c r="AG27" s="81"/>
-      <c r="AH27" s="83" t="inlineStr">
+      <c r="AB27" s="177"/>
+      <c r="AC27" s="177"/>
+      <c r="AD27" s="177"/>
+      <c r="AE27" s="177"/>
+      <c r="AF27" s="177"/>
+      <c r="AG27" s="177"/>
+      <c r="AH27" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0011 Requirement Description and Verification Criteria
 sibling axis: failure handling
@@ -10492,51 +10511,51 @@
       </c>
     </row>
     <row r="28" spans="1:34">
-      <c r="A28" s="87"/>
-      <c r="B28" s="81" t="str">
+      <c r="A28" s="182"/>
+      <c r="B28" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C28" s="82"/>
-      <c r="D28" s="81" t="inlineStr">
+      <c r="C28" s="178"/>
+      <c r="D28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0012</t>
         </is>
       </c>
-      <c r="E28" s="81"/>
-      <c r="F28" s="81" t="inlineStr">
+      <c r="E28" s="177"/>
+      <c r="F28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-019</t>
         </is>
       </c>
-      <c r="G28" s="81" t="inlineStr">
+      <c r="G28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H28" s="81" t="inlineStr">
+      <c r="H28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Verification</t>
         </is>
       </c>
-      <c r="I28" s="81" t="inlineStr">
+      <c r="I28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">"ValidityCounter" is 2byte value(“0”-“65535”),a parameter of configuration file
 (number of ignition cycles is 0 and does not exceed ValidityCounter)</t>
         </is>
       </c>
-      <c r="J28" s="81" t="inlineStr">
+      <c r="J28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K28" s="81" t="inlineStr">
+      <c r="K28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L28" s="81" t="inlineStr">
+      <c r="L28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Read /data/vendor/dauth/vc on the DUT
 $ adb shell cat /data/vendor/dauth/vc
@@ -10546,86 +10565,86 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M28" s="81" t="inlineStr">
+      <c r="M28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The adb shell cat /data/vendor/dauth/vc output shows the ValidityCounter value 0
 2. &lt;observable outcome provided by RD (X-g)&gt;
 3. The adb logcat -s dauth output contains the AuthData in-use entry</t>
         </is>
       </c>
-      <c r="N28" s="81" t="inlineStr">
+      <c r="N28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0012</t>
         </is>
       </c>
-      <c r="O28" s="81" t="inlineStr">
+      <c r="O28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P28" s="81" t="inlineStr">
+      <c r="P28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q28" s="81"/>
-      <c r="R28" s="81" t="inlineStr">
+      <c r="Q28" s="177"/>
+      <c r="R28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">邊界值分析 (Boundary Value Analysis, BVA)</t>
         </is>
       </c>
-      <c r="S28" s="81" t="inlineStr">
+      <c r="S28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T28" s="81" t="inlineStr">
+      <c r="T28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U28" s="81" t="inlineStr">
+      <c r="U28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V28" s="81" t="inlineStr">
+      <c r="V28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W28" s="81" t="inlineStr">
+      <c r="W28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X28" s="83" t="inlineStr">
+      <c r="X28" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y28" s="81" t="inlineStr">
+      <c r="Y28" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z28" s="83" t="inlineStr">
+      <c r="Z28" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA28" s="83" t="inlineStr">
+      <c r="AA28" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB28" s="81"/>
-      <c r="AC28" s="81"/>
-      <c r="AD28" s="81"/>
-      <c r="AE28" s="81"/>
-      <c r="AF28" s="81"/>
-      <c r="AG28" s="81"/>
-      <c r="AH28" s="83" t="inlineStr">
+      <c r="AB28" s="177"/>
+      <c r="AC28" s="177"/>
+      <c r="AD28" s="177"/>
+      <c r="AE28" s="177"/>
+      <c r="AF28" s="177"/>
+      <c r="AG28" s="177"/>
+      <c r="AH28" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0012 Requirement Description and Verification Criteria
 sibling axis: ValidityCounter boundary
@@ -10636,51 +10655,51 @@
       </c>
     </row>
     <row r="29" spans="1:34">
-      <c r="A29" s="87"/>
-      <c r="B29" s="81" t="str">
+      <c r="A29" s="182"/>
+      <c r="B29" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C29" s="82"/>
-      <c r="D29" s="81" t="inlineStr">
+      <c r="C29" s="178"/>
+      <c r="D29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0012</t>
         </is>
       </c>
-      <c r="E29" s="81"/>
-      <c r="F29" s="81" t="inlineStr">
+      <c r="E29" s="177"/>
+      <c r="F29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-020</t>
         </is>
       </c>
-      <c r="G29" s="81" t="inlineStr">
+      <c r="G29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H29" s="81" t="inlineStr">
+      <c r="H29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Verification</t>
         </is>
       </c>
-      <c r="I29" s="81" t="inlineStr">
+      <c r="I29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">"ValidityCounter" is 2byte value(“0”-“65535”),a parameter of configuration file
 (number of ignition cycles is 1 and does not exceed ValidityCounter)</t>
         </is>
       </c>
-      <c r="J29" s="81" t="inlineStr">
+      <c r="J29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K29" s="81" t="inlineStr">
+      <c r="K29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L29" s="81" t="inlineStr">
+      <c r="L29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Read /data/vendor/dauth/vc on the DUT
 $ adb shell cat /data/vendor/dauth/vc
@@ -10690,86 +10709,86 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M29" s="81" t="inlineStr">
+      <c r="M29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The adb shell cat /data/vendor/dauth/vc output shows the ValidityCounter value 1
 2. &lt;observable outcome provided by RD (X-g)&gt;
 3. The adb logcat -s dauth output contains the AuthData in-use entry</t>
         </is>
       </c>
-      <c r="N29" s="81" t="inlineStr">
+      <c r="N29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0012</t>
         </is>
       </c>
-      <c r="O29" s="81" t="inlineStr">
+      <c r="O29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P29" s="81" t="inlineStr">
+      <c r="P29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q29" s="81"/>
-      <c r="R29" s="81" t="inlineStr">
+      <c r="Q29" s="177"/>
+      <c r="R29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">邊界值分析 (Boundary Value Analysis, BVA)</t>
         </is>
       </c>
-      <c r="S29" s="81" t="inlineStr">
+      <c r="S29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T29" s="81" t="inlineStr">
+      <c r="T29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U29" s="81" t="inlineStr">
+      <c r="U29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V29" s="81" t="inlineStr">
+      <c r="V29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W29" s="81" t="inlineStr">
+      <c r="W29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X29" s="83" t="inlineStr">
+      <c r="X29" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y29" s="81" t="inlineStr">
+      <c r="Y29" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z29" s="83" t="inlineStr">
+      <c r="Z29" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA29" s="83" t="inlineStr">
+      <c r="AA29" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB29" s="81"/>
-      <c r="AC29" s="81"/>
-      <c r="AD29" s="81"/>
-      <c r="AE29" s="81"/>
-      <c r="AF29" s="81"/>
-      <c r="AG29" s="81"/>
-      <c r="AH29" s="83" t="inlineStr">
+      <c r="AB29" s="177"/>
+      <c r="AC29" s="177"/>
+      <c r="AD29" s="177"/>
+      <c r="AE29" s="177"/>
+      <c r="AF29" s="177"/>
+      <c r="AG29" s="177"/>
+      <c r="AH29" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0012 Requirement Description and Verification Criteria
 sibling axis: ValidityCounter boundary
@@ -10780,51 +10799,51 @@
       </c>
     </row>
     <row r="30" spans="1:34">
-      <c r="A30" s="87"/>
-      <c r="B30" s="81" t="str">
+      <c r="A30" s="182"/>
+      <c r="B30" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C30" s="82"/>
-      <c r="D30" s="81" t="inlineStr">
+      <c r="C30" s="178"/>
+      <c r="D30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0012</t>
         </is>
       </c>
-      <c r="E30" s="81"/>
-      <c r="F30" s="81" t="inlineStr">
+      <c r="E30" s="177"/>
+      <c r="F30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-021</t>
         </is>
       </c>
-      <c r="G30" s="81" t="inlineStr">
+      <c r="G30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H30" s="81" t="inlineStr">
+      <c r="H30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">AuthData Verification</t>
         </is>
       </c>
-      <c r="I30" s="81" t="inlineStr">
+      <c r="I30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">"ValidityCounter" is 2byte value(“0”-“65535”),a parameter of configuration file
 (number of ignition cycles reaches 65535 and exceeds ValidityCounter)</t>
         </is>
       </c>
-      <c r="J30" s="81" t="inlineStr">
+      <c r="J30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K30" s="81" t="inlineStr">
+      <c r="K30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L30" s="81" t="inlineStr">
+      <c r="L30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Read /data/vendor/dauth/vc on the DUT
 $ adb shell cat /data/vendor/dauth/vc
@@ -10832,85 +10851,85 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M30" s="81" t="inlineStr">
+      <c r="M30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The adb shell cat /data/vendor/dauth/vc output shows the ValidityCounter value 65535
 2. &lt;log keyword provided by RD (X-h)&gt;</t>
         </is>
       </c>
-      <c r="N30" s="81" t="inlineStr">
+      <c r="N30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0012</t>
         </is>
       </c>
-      <c r="O30" s="81" t="inlineStr">
+      <c r="O30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P30" s="81" t="inlineStr">
+      <c r="P30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q30" s="81"/>
-      <c r="R30" s="81" t="inlineStr">
+      <c r="Q30" s="177"/>
+      <c r="R30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">邊界值分析 (Boundary Value Analysis, BVA)</t>
         </is>
       </c>
-      <c r="S30" s="81" t="inlineStr">
+      <c r="S30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T30" s="81" t="inlineStr">
+      <c r="T30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U30" s="81" t="inlineStr">
+      <c r="U30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V30" s="81" t="inlineStr">
+      <c r="V30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W30" s="81" t="inlineStr">
+      <c r="W30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X30" s="83" t="inlineStr">
+      <c r="X30" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y30" s="81" t="inlineStr">
+      <c r="Y30" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z30" s="83" t="inlineStr">
+      <c r="Z30" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA30" s="83" t="inlineStr">
+      <c r="AA30" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB30" s="81"/>
-      <c r="AC30" s="81"/>
-      <c r="AD30" s="81"/>
-      <c r="AE30" s="81"/>
-      <c r="AF30" s="81"/>
-      <c r="AG30" s="81"/>
-      <c r="AH30" s="83" t="inlineStr">
+      <c r="AB30" s="177"/>
+      <c r="AC30" s="177"/>
+      <c r="AD30" s="177"/>
+      <c r="AE30" s="177"/>
+      <c r="AF30" s="177"/>
+      <c r="AG30" s="177"/>
+      <c r="AH30" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0012 Requirement Description and Verification Criteria
 sibling axis: ValidityCounter boundary
@@ -11200,51 +11219,51 @@
       </c>
     </row>
     <row r="33" spans="1:34">
-      <c r="A33" s="87"/>
-      <c r="B33" s="81" t="str">
+      <c r="A33" s="182"/>
+      <c r="B33" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C33" s="82"/>
-      <c r="D33" s="81" t="inlineStr">
+      <c r="C33" s="178"/>
+      <c r="D33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0013</t>
         </is>
       </c>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81" t="inlineStr">
+      <c r="E33" s="177"/>
+      <c r="F33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-024</t>
         </is>
       </c>
-      <c r="G33" s="81" t="inlineStr">
+      <c r="G33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H33" s="81" t="inlineStr">
+      <c r="H33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Target Notification</t>
         </is>
       </c>
-      <c r="I33" s="81" t="inlineStr">
+      <c r="I33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">OFF message has to be sent to all connected clients on boot or resume from suspend
 (head unit resumes from suspend on Atl-Hi; disabling is notified)</t>
         </is>
       </c>
-      <c r="J33" s="81" t="inlineStr">
+      <c r="J33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K33" s="81" t="inlineStr">
+      <c r="K33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L33" s="81" t="inlineStr">
+      <c r="L33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;suspend/resume trigger method provided by RD (X-n)&gt; is executed
 $ &lt;command provided by RD (X-n)&gt;
@@ -11252,85 +11271,85 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M33" s="81" t="inlineStr">
+      <c r="M33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;suspend/resume trigger method provided by RD (X-n)&gt;
 2. The adb logcat -s dauth output contains the OFF notification to the target functions</t>
         </is>
       </c>
-      <c r="N33" s="81" t="inlineStr">
+      <c r="N33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0013</t>
         </is>
       </c>
-      <c r="O33" s="81" t="inlineStr">
+      <c r="O33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P33" s="81" t="inlineStr">
+      <c r="P33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q33" s="81"/>
-      <c r="R33" s="81" t="inlineStr">
+      <c r="Q33" s="177"/>
+      <c r="R33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">狀態轉換 (State Transition Testing)</t>
         </is>
       </c>
-      <c r="S33" s="81" t="inlineStr">
+      <c r="S33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T33" s="81" t="inlineStr">
+      <c r="T33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U33" s="81" t="inlineStr">
+      <c r="U33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V33" s="81" t="inlineStr">
+      <c r="V33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="W33" s="81" t="inlineStr">
+      <c r="W33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X33" s="83" t="inlineStr">
+      <c r="X33" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y33" s="81" t="inlineStr">
+      <c r="Y33" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Z33" s="83" t="inlineStr">
+      <c r="Z33" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="AA33" s="83" t="inlineStr">
+      <c r="AA33" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB33" s="81"/>
-      <c r="AC33" s="81"/>
-      <c r="AD33" s="81"/>
-      <c r="AE33" s="81"/>
-      <c r="AF33" s="81"/>
-      <c r="AG33" s="81"/>
-      <c r="AH33" s="83" t="inlineStr">
+      <c r="AB33" s="177"/>
+      <c r="AC33" s="177"/>
+      <c r="AD33" s="177"/>
+      <c r="AE33" s="177"/>
+      <c r="AF33" s="177"/>
+      <c r="AG33" s="177"/>
+      <c r="AH33" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0013 Requirement Description and Verification Criteria
 sibling axis: EE architecture
@@ -11341,51 +11360,51 @@
       </c>
     </row>
     <row r="34" spans="1:34">
-      <c r="A34" s="87"/>
-      <c r="B34" s="81" t="str">
+      <c r="A34" s="182"/>
+      <c r="B34" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C34" s="82"/>
-      <c r="D34" s="81" t="inlineStr">
+      <c r="C34" s="178"/>
+      <c r="D34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0013</t>
         </is>
       </c>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81" t="inlineStr">
+      <c r="E34" s="177"/>
+      <c r="F34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-025</t>
         </is>
       </c>
-      <c r="G34" s="81" t="inlineStr">
+      <c r="G34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H34" s="81" t="inlineStr">
+      <c r="H34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Target Notification</t>
         </is>
       </c>
-      <c r="I34" s="81" t="inlineStr">
+      <c r="I34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">OFF message has to be sent to all connected clients on boot or resume from suspend
 (head unit resumes from suspend on Atl-Mi; disabling is notified)</t>
         </is>
       </c>
-      <c r="J34" s="81" t="inlineStr">
+      <c r="J34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K34" s="81" t="inlineStr">
+      <c r="K34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L34" s="81" t="inlineStr">
+      <c r="L34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;suspend/resume trigger method provided by RD (X-n)&gt; is executed
 $ &lt;command provided by RD (X-n)&gt;
@@ -11393,85 +11412,85 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M34" s="81" t="inlineStr">
+      <c r="M34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;suspend/resume trigger method provided by RD (X-n)&gt;
 2. The adb logcat -s dauth output contains the OFF notification to the target functions</t>
         </is>
       </c>
-      <c r="N34" s="81" t="inlineStr">
+      <c r="N34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0013</t>
         </is>
       </c>
-      <c r="O34" s="81" t="inlineStr">
+      <c r="O34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P34" s="81" t="inlineStr">
+      <c r="P34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q34" s="81"/>
-      <c r="R34" s="81" t="inlineStr">
+      <c r="Q34" s="177"/>
+      <c r="R34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">狀態轉換 (State Transition Testing)</t>
         </is>
       </c>
-      <c r="S34" s="81" t="inlineStr">
+      <c r="S34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T34" s="81" t="inlineStr">
+      <c r="T34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="U34" s="81" t="inlineStr">
+      <c r="U34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="V34" s="81" t="inlineStr">
+      <c r="V34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W34" s="81" t="inlineStr">
+      <c r="W34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X34" s="83" t="inlineStr">
+      <c r="X34" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y34" s="81" t="inlineStr">
+      <c r="Y34" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z34" s="83" t="inlineStr">
+      <c r="Z34" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA34" s="83" t="inlineStr">
+      <c r="AA34" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB34" s="81"/>
-      <c r="AC34" s="81"/>
-      <c r="AD34" s="81"/>
-      <c r="AE34" s="81"/>
-      <c r="AF34" s="81"/>
-      <c r="AG34" s="81"/>
-      <c r="AH34" s="83" t="inlineStr">
+      <c r="AB34" s="177"/>
+      <c r="AC34" s="177"/>
+      <c r="AD34" s="177"/>
+      <c r="AE34" s="177"/>
+      <c r="AF34" s="177"/>
+      <c r="AG34" s="177"/>
+      <c r="AH34" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0013 Requirement Description and Verification Criteria
 sibling axis: EE architecture
@@ -11482,50 +11501,51 @@
       </c>
     </row>
     <row r="35" spans="1:34">
-      <c r="B35" s="81" t="str">
+      <c r="A35" s="176"/>
+      <c r="B35" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C35" s="82"/>
-      <c r="D35" s="81" t="inlineStr">
+      <c r="C35" s="178"/>
+      <c r="D35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0014</t>
         </is>
       </c>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81" t="inlineStr">
+      <c r="E35" s="177"/>
+      <c r="F35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-026</t>
         </is>
       </c>
-      <c r="G35" s="81" t="inlineStr">
+      <c r="G35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H35" s="81" t="inlineStr">
+      <c r="H35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Target Notification</t>
         </is>
       </c>
-      <c r="I35" s="81" t="inlineStr">
+      <c r="I35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">This function gives SAM target functions a permission to be active only if all the AuthData verification steps pass
 (verification succeeds; the target functions are notified according to SAMType)</t>
         </is>
       </c>
-      <c r="J35" s="81" t="inlineStr">
+      <c r="J35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K35" s="81" t="inlineStr">
+      <c r="K35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L35" s="81" t="inlineStr">
+      <c r="L35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;DUT-side trigger for SAM AuthData package that passes verification provided by RD (X-g)&gt;
 $ &lt;command provided by RD (X-g)&gt;
@@ -11533,85 +11553,85 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M35" s="81" t="inlineStr">
+      <c r="M35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;observable outcome provided by RD (X-g)&gt;
 2. The adb logcat -s dauth output contains the ON notification to the target functions</t>
         </is>
       </c>
-      <c r="N35" s="81" t="inlineStr">
+      <c r="N35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0014</t>
         </is>
       </c>
-      <c r="O35" s="81" t="inlineStr">
+      <c r="O35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P35" s="81" t="inlineStr">
+      <c r="P35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q35" s="81"/>
-      <c r="R35" s="81" t="inlineStr">
+      <c r="Q35" s="177"/>
+      <c r="R35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S35" s="81" t="inlineStr">
+      <c r="S35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T35" s="81" t="inlineStr">
+      <c r="T35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U35" s="81" t="inlineStr">
+      <c r="U35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V35" s="81" t="inlineStr">
+      <c r="V35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W35" s="81" t="inlineStr">
+      <c r="W35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X35" s="83" t="inlineStr">
+      <c r="X35" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y35" s="81" t="inlineStr">
+      <c r="Y35" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z35" s="83" t="inlineStr">
+      <c r="Z35" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA35" s="83" t="inlineStr">
+      <c r="AA35" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB35" s="81"/>
-      <c r="AC35" s="81"/>
-      <c r="AD35" s="81"/>
-      <c r="AE35" s="81"/>
-      <c r="AF35" s="81"/>
-      <c r="AG35" s="81"/>
-      <c r="AH35" s="83" t="inlineStr">
+      <c r="AB35" s="177"/>
+      <c r="AC35" s="177"/>
+      <c r="AD35" s="177"/>
+      <c r="AE35" s="177"/>
+      <c r="AF35" s="177"/>
+      <c r="AG35" s="177"/>
+      <c r="AH35" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0014 Requirement Description and Verification Criteria
 sibling axis: notification trigger
@@ -11622,50 +11642,51 @@
       </c>
     </row>
     <row r="36" spans="1:34">
-      <c r="B36" s="81" t="str">
+      <c r="A36" s="176"/>
+      <c r="B36" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C36" s="82"/>
-      <c r="D36" s="81" t="inlineStr">
+      <c r="C36" s="178"/>
+      <c r="D36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0015</t>
         </is>
       </c>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81" t="inlineStr">
+      <c r="E36" s="177"/>
+      <c r="F36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-027</t>
         </is>
       </c>
-      <c r="G36" s="81" t="inlineStr">
+      <c r="G36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H36" s="81" t="inlineStr">
+      <c r="H36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Target Notification</t>
         </is>
       </c>
-      <c r="I36" s="81" t="inlineStr">
+      <c r="I36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">In order to know the notifications sequence received by the target functions, DebugAuth includes the sequence ID into the notification message.
 (sequence ID is included, logged and incremented when a status message is sent)</t>
         </is>
       </c>
-      <c r="J36" s="81" t="inlineStr">
+      <c r="J36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. DebugAuth is running on the DUT</t>
         </is>
       </c>
-      <c r="K36" s="81" t="inlineStr">
+      <c r="K36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L36" s="81" t="inlineStr">
+      <c r="L36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Clear the log buffer before the status message is sent
 $ adb logcat -c
@@ -11679,7 +11700,7 @@
 $ adb shell cat /data/vendor/dauth/seqId</t>
         </is>
       </c>
-      <c r="M36" s="81" t="inlineStr">
+      <c r="M36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The log buffer is cleared
 2. The adb shell cat /data/vendor/dauth/seqId output shows the current sequence ID
@@ -11688,79 +11709,79 @@
 5. The adb shell cat /data/vendor/dauth/seqId output shows the incremented sequence ID</t>
         </is>
       </c>
-      <c r="N36" s="81" t="inlineStr">
+      <c r="N36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0015</t>
         </is>
       </c>
-      <c r="O36" s="81" t="inlineStr">
+      <c r="O36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P36" s="81" t="inlineStr">
+      <c r="P36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q36" s="81"/>
-      <c r="R36" s="81" t="inlineStr">
+      <c r="Q36" s="177"/>
+      <c r="R36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S36" s="81" t="inlineStr">
+      <c r="S36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T36" s="81" t="inlineStr">
+      <c r="T36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U36" s="81" t="inlineStr">
+      <c r="U36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V36" s="81" t="inlineStr">
+      <c r="V36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W36" s="81" t="inlineStr">
+      <c r="W36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X36" s="83" t="inlineStr">
+      <c r="X36" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y36" s="81" t="inlineStr">
+      <c r="Y36" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z36" s="83" t="inlineStr">
+      <c r="Z36" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA36" s="83" t="inlineStr">
+      <c r="AA36" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB36" s="81"/>
-      <c r="AC36" s="81"/>
-      <c r="AD36" s="81"/>
-      <c r="AE36" s="81"/>
-      <c r="AF36" s="81"/>
-      <c r="AG36" s="81"/>
-      <c r="AH36" s="83" t="inlineStr">
+      <c r="AB36" s="177"/>
+      <c r="AC36" s="177"/>
+      <c r="AD36" s="177"/>
+      <c r="AE36" s="177"/>
+      <c r="AF36" s="177"/>
+      <c r="AG36" s="177"/>
+      <c r="AH36" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0015 Requirement Description and Verification Criteria
 sibling axis: message content; rule 1,4 of SEC-04 4.2
@@ -11771,50 +11792,51 @@
       </c>
     </row>
     <row r="37" spans="1:34">
-      <c r="B37" s="81" t="str">
+      <c r="A37" s="176"/>
+      <c r="B37" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C37" s="82"/>
-      <c r="D37" s="81" t="inlineStr">
+      <c r="C37" s="178"/>
+      <c r="D37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0016</t>
         </is>
       </c>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81" t="inlineStr">
+      <c r="E37" s="177"/>
+      <c r="F37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-028</t>
         </is>
       </c>
-      <c r="G37" s="81" t="inlineStr">
+      <c r="G37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H37" s="81" t="inlineStr">
+      <c r="H37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Target Notification</t>
         </is>
       </c>
-      <c r="I37" s="81" t="inlineStr">
+      <c r="I37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">DebugAuth sends ON if AuthData is applied and connected target function is relevant for SAMType.
 (target function connects while the status is ON; the current status is notified)</t>
         </is>
       </c>
-      <c r="J37" s="81" t="inlineStr">
+      <c r="J37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K37" s="81" t="inlineStr">
+      <c r="K37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L37" s="81" t="inlineStr">
+      <c r="L37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;DUT-side trigger for SAM AuthData target function connection provided by RD (X-g)&gt;
 $ &lt;command provided by RD (X-g)&gt;
@@ -11822,85 +11844,85 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M37" s="81" t="inlineStr">
+      <c r="M37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;observable outcome provided by RD (X-g)&gt;
 2. The adb logcat -s dauth output contains the current status notification</t>
         </is>
       </c>
-      <c r="N37" s="81" t="inlineStr">
+      <c r="N37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0016</t>
         </is>
       </c>
-      <c r="O37" s="81" t="inlineStr">
+      <c r="O37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P37" s="81" t="inlineStr">
+      <c r="P37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q37" s="81"/>
-      <c r="R37" s="81" t="inlineStr">
+      <c r="Q37" s="177"/>
+      <c r="R37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S37" s="81" t="inlineStr">
+      <c r="S37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T37" s="81" t="inlineStr">
+      <c r="T37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U37" s="81" t="inlineStr">
+      <c r="U37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V37" s="81" t="inlineStr">
+      <c r="V37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W37" s="81" t="inlineStr">
+      <c r="W37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X37" s="83" t="inlineStr">
+      <c r="X37" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y37" s="81" t="inlineStr">
+      <c r="Y37" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z37" s="83" t="inlineStr">
+      <c r="Z37" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA37" s="83" t="inlineStr">
+      <c r="AA37" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB37" s="81"/>
-      <c r="AC37" s="81"/>
-      <c r="AD37" s="81"/>
-      <c r="AE37" s="81"/>
-      <c r="AF37" s="81"/>
-      <c r="AG37" s="81"/>
-      <c r="AH37" s="83" t="inlineStr">
+      <c r="AB37" s="177"/>
+      <c r="AC37" s="177"/>
+      <c r="AD37" s="177"/>
+      <c r="AE37" s="177"/>
+      <c r="AF37" s="177"/>
+      <c r="AG37" s="177"/>
+      <c r="AH37" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0016 Requirement Description and Verification Criteria
 sibling axis: current status
@@ -11911,50 +11933,51 @@
       </c>
     </row>
     <row r="38" spans="1:34">
-      <c r="B38" s="81" t="str">
+      <c r="A38" s="176"/>
+      <c r="B38" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C38" s="82"/>
-      <c r="D38" s="81" t="inlineStr">
+      <c r="C38" s="178"/>
+      <c r="D38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-0016</t>
         </is>
       </c>
-      <c r="E38" s="81"/>
-      <c r="F38" s="81" t="inlineStr">
+      <c r="E38" s="177"/>
+      <c r="F38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SAM-029</t>
         </is>
       </c>
-      <c r="G38" s="81" t="inlineStr">
+      <c r="G38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SAM</t>
         </is>
       </c>
-      <c r="H38" s="81" t="inlineStr">
+      <c r="H38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Target Notification</t>
         </is>
       </c>
-      <c r="I38" s="81" t="inlineStr">
+      <c r="I38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">DebugAuth sends ON if AuthData is applied and connected target function is relevant for SAMType.
 (target function connects while the status is OFF; the current status is notified)</t>
         </is>
       </c>
-      <c r="J38" s="81" t="inlineStr">
+      <c r="J38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. SAM dongle is inserted into the DUT</t>
         </is>
       </c>
-      <c r="K38" s="81" t="inlineStr">
+      <c r="K38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L38" s="81" t="inlineStr">
+      <c r="L38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;DUT-side trigger for SAM AuthData target function connection provided by RD (X-g)&gt;
 $ &lt;command provided by RD (X-g)&gt;
@@ -11962,85 +11985,85 @@
 $ adb logcat -s dauth</t>
         </is>
       </c>
-      <c r="M38" s="81" t="inlineStr">
+      <c r="M38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;observable outcome provided by RD (X-g)&gt;
 2. The adb logcat -s dauth output contains the current status notification</t>
         </is>
       </c>
-      <c r="N38" s="81" t="inlineStr">
+      <c r="N38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0016</t>
         </is>
       </c>
-      <c r="O38" s="81" t="inlineStr">
+      <c r="O38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P38" s="81" t="inlineStr">
+      <c r="P38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="Q38" s="81"/>
-      <c r="R38" s="81" t="inlineStr">
+      <c r="Q38" s="177"/>
+      <c r="R38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S38" s="81" t="inlineStr">
+      <c r="S38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T38" s="81" t="inlineStr">
+      <c r="T38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U38" s="81" t="inlineStr">
+      <c r="U38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V38" s="81" t="inlineStr">
+      <c r="V38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W38" s="81" t="inlineStr">
+      <c r="W38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X38" s="83" t="inlineStr">
+      <c r="X38" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y38" s="81" t="inlineStr">
+      <c r="Y38" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z38" s="83" t="inlineStr">
+      <c r="Z38" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA38" s="83" t="inlineStr">
+      <c r="AA38" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB38" s="81"/>
-      <c r="AC38" s="81"/>
-      <c r="AD38" s="81"/>
-      <c r="AE38" s="81"/>
-      <c r="AF38" s="81"/>
-      <c r="AG38" s="81"/>
-      <c r="AH38" s="83" t="inlineStr">
+      <c r="AB38" s="177"/>
+      <c r="AC38" s="177"/>
+      <c r="AD38" s="177"/>
+      <c r="AE38" s="177"/>
+      <c r="AF38" s="177"/>
+      <c r="AG38" s="177"/>
+      <c r="AH38" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SAM-0016 Requirement Description and Verification Criteria
 sibling axis: current status

--- a/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SAM_20260917.xlsx
+++ b/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SAM_20260917.xlsx
@@ -8003,7 +8003,9 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0001</t>
+          <t xml:space="preserve">CFTS084-134367
+CFTS084-134383
+CFTS084-134384</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8140,7 +8142,9 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0002</t>
+          <t xml:space="preserve">CFTS084-134367
+CFTS084-134383
+CFTS084-134384</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8278,7 +8282,10 @@
       </c>
       <c r="N12" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0003</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O12" s="177" t="inlineStr">
@@ -8418,7 +8425,10 @@
       </c>
       <c r="N13" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0003</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O13" s="177" t="inlineStr">
@@ -8569,7 +8579,10 @@
       </c>
       <c r="N14" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0004</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O14" s="177" t="inlineStr">
@@ -8716,7 +8729,10 @@
       </c>
       <c r="N15" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0005</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O15" s="177" t="inlineStr">
@@ -8857,7 +8873,10 @@
       </c>
       <c r="N16" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0005</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O16" s="177" t="inlineStr">
@@ -9002,7 +9021,10 @@
       </c>
       <c r="N17" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0006</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O17" s="177" t="inlineStr">
@@ -9143,7 +9165,10 @@
       </c>
       <c r="N18" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0006</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O18" s="177" t="inlineStr">
@@ -9290,7 +9315,10 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0007</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9435,7 +9463,10 @@
       </c>
       <c r="N20" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0007</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O20" s="177" t="inlineStr">
@@ -9576,7 +9607,10 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0008</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">
@@ -9715,7 +9749,10 @@
       </c>
       <c r="N22" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0008</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O22" s="177" t="inlineStr">
@@ -9857,7 +9894,9 @@
       </c>
       <c r="N23" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0009</t>
+          <t xml:space="preserve">CFTS084-134372
+CFTS084-134373
+CFTS084-134374</t>
         </is>
       </c>
       <c r="O23" s="177" t="inlineStr">
@@ -9998,7 +10037,9 @@
       </c>
       <c r="N24" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0009</t>
+          <t xml:space="preserve">CFTS084-134372
+CFTS084-134373
+CFTS084-134374</t>
         </is>
       </c>
       <c r="O24" s="177" t="inlineStr">
@@ -10142,7 +10183,9 @@
       </c>
       <c r="N25" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0010</t>
+          <t xml:space="preserve">CFTS084-134372
+CFTS084-134373
+CFTS084-134374</t>
         </is>
       </c>
       <c r="O25" s="177" t="inlineStr">
@@ -10286,7 +10329,9 @@
       </c>
       <c r="N26" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0010</t>
+          <t xml:space="preserve">CFTS084-134372
+CFTS084-134373
+CFTS084-134374</t>
         </is>
       </c>
       <c r="O26" s="177" t="inlineStr">
@@ -10430,7 +10475,7 @@
       </c>
       <c r="N27" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0011</t>
+          <t xml:space="preserve">CFTS084-134368</t>
         </is>
       </c>
       <c r="O27" s="177" t="inlineStr">
@@ -10574,7 +10619,7 @@
       </c>
       <c r="N28" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0012</t>
+          <t xml:space="preserve">CFTS084-134386</t>
         </is>
       </c>
       <c r="O28" s="177" t="inlineStr">
@@ -10718,7 +10763,7 @@
       </c>
       <c r="N29" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0012</t>
+          <t xml:space="preserve">CFTS084-134386</t>
         </is>
       </c>
       <c r="O29" s="177" t="inlineStr">
@@ -10859,7 +10904,7 @@
       </c>
       <c r="N30" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0012</t>
+          <t xml:space="preserve">CFTS084-134386</t>
         </is>
       </c>
       <c r="O30" s="177" t="inlineStr">
@@ -10999,7 +11044,7 @@
       </c>
       <c r="N31" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0013</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O31" s="81" t="inlineStr">
@@ -11139,7 +11184,7 @@
       </c>
       <c r="N32" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0013</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O32" s="81" t="inlineStr">
@@ -11279,7 +11324,7 @@
       </c>
       <c r="N33" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0013</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O33" s="177" t="inlineStr">
@@ -11420,7 +11465,7 @@
       </c>
       <c r="N34" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0013</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O34" s="177" t="inlineStr">
@@ -11561,7 +11606,7 @@
       </c>
       <c r="N35" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0014</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O35" s="177" t="inlineStr">
@@ -11711,7 +11756,7 @@
       </c>
       <c r="N36" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0015</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O36" s="177" t="inlineStr">
@@ -11852,7 +11897,7 @@
       </c>
       <c r="N37" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0016</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O37" s="177" t="inlineStr">
@@ -11993,7 +12038,7 @@
       </c>
       <c r="N38" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0016</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O38" s="177" t="inlineStr">
@@ -12133,7 +12178,7 @@
       </c>
       <c r="N39" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0017</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O39" s="81" t="inlineStr">
@@ -12272,7 +12317,7 @@
       </c>
       <c r="N40" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0017</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O40" s="81" t="inlineStr">
@@ -12411,7 +12456,9 @@
       </c>
       <c r="N41" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0018</t>
+          <t xml:space="preserve">CFTS084-134367
+CFTS084-134383
+CFTS084-134384</t>
         </is>
       </c>
       <c r="O41" s="81" t="inlineStr">
@@ -12546,7 +12593,9 @@
       </c>
       <c r="N42" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0019</t>
+          <t xml:space="preserve">CFTS084-134367
+CFTS084-134383
+CFTS084-134384</t>
         </is>
       </c>
       <c r="O42" s="81" t="inlineStr">

--- a/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SAM_20260917.xlsx
+++ b/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SAM_20260917.xlsx
@@ -8003,9 +8003,9 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134367
-CFTS084-134383
-CFTS084-134384</t>
+          <t xml:space="preserve">CFTS084-4949332
+CFTS084-4949351
+CFTS084-4949352</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8142,9 +8142,9 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134367
-CFTS084-134383
-CFTS084-134384</t>
+          <t xml:space="preserve">CFTS084-4949332
+CFTS084-4949351
+CFTS084-4949352</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8282,10 +8282,10 @@
       </c>
       <c r="N12" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O12" s="177" t="inlineStr">
@@ -8425,10 +8425,10 @@
       </c>
       <c r="N13" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O13" s="177" t="inlineStr">
@@ -8579,10 +8579,10 @@
       </c>
       <c r="N14" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O14" s="177" t="inlineStr">
@@ -8729,10 +8729,10 @@
       </c>
       <c r="N15" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O15" s="177" t="inlineStr">
@@ -8873,10 +8873,10 @@
       </c>
       <c r="N16" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O16" s="177" t="inlineStr">
@@ -9021,10 +9021,10 @@
       </c>
       <c r="N17" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O17" s="177" t="inlineStr">
@@ -9165,10 +9165,10 @@
       </c>
       <c r="N18" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O18" s="177" t="inlineStr">
@@ -9315,10 +9315,10 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9463,10 +9463,10 @@
       </c>
       <c r="N20" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O20" s="177" t="inlineStr">
@@ -9607,10 +9607,10 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">
@@ -9749,10 +9749,10 @@
       </c>
       <c r="N22" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O22" s="177" t="inlineStr">
@@ -9894,9 +9894,9 @@
       </c>
       <c r="N23" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134372
-CFTS084-134373
-CFTS084-134374</t>
+          <t xml:space="preserve">CFTS084-4949338
+CFTS084-4949339
+CFTS084-4949340</t>
         </is>
       </c>
       <c r="O23" s="177" t="inlineStr">
@@ -10037,9 +10037,9 @@
       </c>
       <c r="N24" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134372
-CFTS084-134373
-CFTS084-134374</t>
+          <t xml:space="preserve">CFTS084-4949338
+CFTS084-4949339
+CFTS084-4949340</t>
         </is>
       </c>
       <c r="O24" s="177" t="inlineStr">
@@ -10183,9 +10183,9 @@
       </c>
       <c r="N25" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134372
-CFTS084-134373
-CFTS084-134374</t>
+          <t xml:space="preserve">CFTS084-4949338
+CFTS084-4949339
+CFTS084-4949340</t>
         </is>
       </c>
       <c r="O25" s="177" t="inlineStr">
@@ -10329,9 +10329,9 @@
       </c>
       <c r="N26" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134372
-CFTS084-134373
-CFTS084-134374</t>
+          <t xml:space="preserve">CFTS084-4949338
+CFTS084-4949339
+CFTS084-4949340</t>
         </is>
       </c>
       <c r="O26" s="177" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="N27" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134368</t>
+          <t xml:space="preserve">CFTS084-4949333</t>
         </is>
       </c>
       <c r="O27" s="177" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="N28" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134386</t>
+          <t xml:space="preserve">CFTS084-4949354</t>
         </is>
       </c>
       <c r="O28" s="177" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="N29" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134386</t>
+          <t xml:space="preserve">CFTS084-4949354</t>
         </is>
       </c>
       <c r="O29" s="177" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="N30" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134386</t>
+          <t xml:space="preserve">CFTS084-4949354</t>
         </is>
       </c>
       <c r="O30" s="177" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="N31" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O31" s="81" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="N32" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O32" s="81" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="N33" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O33" s="177" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="N34" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O34" s="177" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="N35" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O35" s="177" t="inlineStr">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="N36" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O36" s="177" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="N37" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O37" s="177" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="N38" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O38" s="177" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="N39" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O39" s="81" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="N40" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O40" s="81" t="inlineStr">
@@ -12456,9 +12456,9 @@
       </c>
       <c r="N41" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134367
-CFTS084-134383
-CFTS084-134384</t>
+          <t xml:space="preserve">CFTS084-4949332
+CFTS084-4949351
+CFTS084-4949352</t>
         </is>
       </c>
       <c r="O41" s="81" t="inlineStr">
@@ -12593,9 +12593,9 @@
       </c>
       <c r="N42" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134367
-CFTS084-134383
-CFTS084-134384</t>
+          <t xml:space="preserve">CFTS084-4949332
+CFTS084-4949351
+CFTS084-4949352</t>
         </is>
       </c>
       <c r="O42" s="81" t="inlineStr">
